--- a/02_interactive_plots/TIER2_recommendations.xlsx
+++ b/02_interactive_plots/TIER2_recommendations.xlsx
@@ -114,7 +114,7 @@
     <t>Publishers should enhance journal capacity and infrastructure for checking and managing digital research objects</t>
   </si>
   <si>
-    <t>Evidence-based policy</t>
+    <t>Strengthening the evidence-base</t>
   </si>
   <si>
     <t>R4.1.</t>

--- a/02_interactive_plots/TIER2_recommendations.xlsx
+++ b/02_interactive_plots/TIER2_recommendations.xlsx
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Clarify licensing, consent and data-protection conditions for data held or generated at the institution, so that secondary users know what re-use is permitted</t>
+          <t>Track the staff time and costs of institutional reproducibility measures, such as training, support roles and data stewardship, and make these data available to meta-researchers under appropriate access conditions</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Provide data stewardship and legal support to help researchers assess whether and how existing data may be re-used</t>
+          <t>Evaluate the costs and benefits of own training and policy programmes, including unintended effects on researchers' workload, and publish the results</t>
         </is>
       </c>
     </row>
